--- a/逆合成/Materials-stack4列.xlsx
+++ b/逆合成/Materials-stack4列.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\24017\PycharmProjects\pythonProject\接口测试\project\excel_generation\逆合成\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C205403-1337-4FB4-9A47-5A3587A8E854}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="28980" windowHeight="14865" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="PlateStack" sheetId="1" r:id="rId1"/>
@@ -20,12 +14,25 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">HopperStack!$A$1:$C$6</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="72">
   <si>
     <t>Layer</t>
   </si>
@@ -42,79 +49,348 @@
     <t>D列</t>
   </si>
   <si>
+    <t>E列</t>
+  </si>
+  <si>
+    <t>F列</t>
+  </si>
+  <si>
+    <t>G列</t>
+  </si>
+  <si>
     <t>规格设置</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>TA3-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>试剂板</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>-B03</t>
+    </r>
+  </si>
+  <si>
+    <t>TA2-试剂板-B03</t>
+  </si>
+  <si>
     <t>TA1-封膜-产物板-2B01</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>TA1-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>试剂板</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>-B03</t>
+    </r>
+  </si>
+  <si>
+    <t>TA1-枪头_1000ul-A05</t>
+  </si>
+  <si>
+    <t>TA1-枪头_1000ul-B05</t>
+  </si>
+  <si>
+    <t>24孔</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>TA3-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>试剂板</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>-B02</t>
+    </r>
+  </si>
+  <si>
+    <t>TA2-试剂板-B02</t>
+  </si>
+  <si>
     <t>TA1-过滤板-2A01</t>
   </si>
   <si>
-    <t>TA1-磁子分装_2ml-1</t>
-  </si>
-  <si>
-    <t>TA1-称量载具_2ml-1</t>
-  </si>
-  <si>
-    <t>24孔</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>TA1-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>试剂板</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>-B02</t>
+    </r>
+  </si>
+  <si>
+    <t>TA1-枪头_200ul-A04</t>
+  </si>
+  <si>
+    <t>TA1-枪头_200ul-B04</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>TA3-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>试剂板</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>-A03</t>
+    </r>
+  </si>
+  <si>
+    <t>TA2-试剂板-A03</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>TA1-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>磁子分装</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>_8ml-1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>TA1-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>试剂板</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>-A03</t>
+    </r>
+  </si>
+  <si>
+    <t>TA1-金属板-B01</t>
+  </si>
+  <si>
+    <t>TA1-板盖-A01</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>TA3-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>试剂板</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>-A02</t>
+    </r>
+  </si>
+  <si>
+    <t>TA2-试剂板-A02</t>
   </si>
   <si>
     <t>TA1-称量载具_8ml-2</t>
   </si>
   <si>
-    <t>TA1-板盖-A01</t>
-  </si>
-  <si>
-    <t>TA1-金属板-B01</t>
-  </si>
-  <si>
-    <t>TA1-试剂板-A02</t>
-  </si>
-  <si>
-    <t>TA1-试剂板-A03</t>
-  </si>
-  <si>
-    <t>TA1-试剂板-B02</t>
-  </si>
-  <si>
-    <t>TA1-试剂板-B03</t>
-  </si>
-  <si>
-    <t>TA2-试剂板-A02</t>
-  </si>
-  <si>
-    <t>TA2-试剂板-A03</t>
-  </si>
-  <si>
-    <t>TA2-试剂板-B02</t>
-  </si>
-  <si>
-    <t>TA2-试剂板-B03</t>
-  </si>
-  <si>
-    <t>TA3-试剂板-A02</t>
-  </si>
-  <si>
-    <t>TA3-试剂板-A03</t>
-  </si>
-  <si>
-    <t>TA3-试剂板-B02</t>
-  </si>
-  <si>
-    <t>TA3-试剂板-B03</t>
-  </si>
-  <si>
-    <t>TA1-枪头_200ul-A04</t>
-  </si>
-  <si>
-    <t>TA1-枪头_200ul-B04</t>
-  </si>
-  <si>
-    <t>TA1-枪头_1000ul-A05</t>
-  </si>
-  <si>
-    <t>TA1-枪头_1000ul-B05</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>TA1-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>称量载具</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>_8ml-1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>TA1-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>试剂板</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>-A02</t>
+    </r>
   </si>
   <si>
     <t>说明</t>
@@ -229,13 +505,22 @@
   </si>
   <si>
     <t>Hopper5</t>
+  </si>
+  <si>
+    <t>20260710-001</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -246,29 +531,173 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -284,11 +713,203 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -354,16 +975,259 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -372,173 +1236,107 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
+        <b val="1"/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="1"/>
       </font>
       <border>
@@ -549,7 +1347,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="0"/>
       </font>
       <fill>
@@ -577,40 +1375,154 @@
           <color theme="4"/>
         </bottom>
         <horizontal style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
+          <color theme="4" tint="0.399975585192419"/>
         </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
       </border>
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" dxfId="16"/>
-      <tableStyleElement type="headerRow" dxfId="15"/>
-      <tableStyleElement type="totalRow" dxfId="14"/>
-      <tableStyleElement type="firstColumn" dxfId="13"/>
-      <tableStyleElement type="lastColumn" dxfId="12"/>
-      <tableStyleElement type="firstRowStripe" dxfId="11"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="10"/>
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
-      <tableStyleElement type="headerRow" dxfId="9"/>
-      <tableStyleElement type="totalRow" dxfId="8"/>
-      <tableStyleElement type="firstRowStripe" dxfId="7"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="6"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="5"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="4"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="3"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="2"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="1"/>
-      <tableStyleElement type="pageFieldValues" dxfId="0"/>
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
     </tableStyle>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -868,162 +1780,182 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:O35"/>
-  <sheetFormatPr defaultColWidth="10.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="10.2857142857143" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="33.7109375" style="8" customWidth="1"/>
-    <col min="3" max="3" width="21.28515625" style="8" customWidth="1"/>
-    <col min="4" max="4" width="22.28515625" style="8" customWidth="1"/>
-    <col min="5" max="5" width="22.42578125" style="8" customWidth="1"/>
-    <col min="6" max="6" width="21.7109375" style="8" customWidth="1"/>
-    <col min="7" max="9" width="15.28515625" style="8" customWidth="1"/>
-    <col min="10" max="10" width="15.42578125" style="8" customWidth="1"/>
-    <col min="11" max="11" width="12.42578125" style="8" customWidth="1"/>
-    <col min="12" max="12" width="12.5703125" style="8" customWidth="1"/>
-    <col min="13" max="13" width="12.42578125" style="8" customWidth="1"/>
-    <col min="14" max="14" width="17.5703125" style="8" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" style="8" customWidth="1"/>
+    <col min="2" max="2" width="25.2857142857143" style="1" customWidth="1"/>
+    <col min="3" max="3" width="21.7142857142857" style="1" customWidth="1"/>
+    <col min="4" max="4" width="22.2857142857143" style="1" customWidth="1"/>
+    <col min="5" max="5" width="22.4285714285714" style="1" customWidth="1"/>
+    <col min="6" max="6" width="21.7142857142857" style="1" customWidth="1"/>
+    <col min="7" max="7" width="22.4285714285714" style="1" customWidth="1"/>
+    <col min="8" max="8" width="23.2857142857143" style="1" customWidth="1"/>
+    <col min="9" max="9" width="15.2857142857143" style="1" customWidth="1"/>
+    <col min="10" max="10" width="15.4285714285714" style="1" customWidth="1"/>
+    <col min="11" max="11" width="12.4285714285714" style="1" customWidth="1"/>
+    <col min="12" max="12" width="12.5714285714286" style="1" customWidth="1"/>
+    <col min="13" max="13" width="12.4285714285714" style="1" customWidth="1"/>
+    <col min="14" max="14" width="17.5714285714286" style="1" customWidth="1"/>
+    <col min="15" max="15" width="14.2857142857143" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:15">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="8" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="4">
+      <c r="G1" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" ht="16.5" customHeight="1" spans="1:15">
+      <c r="A2" s="5">
         <v>1</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="5"/>
+      <c r="E2" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="I2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
+      <c r="A3" s="5">
+        <v>2</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="5"/>
+      <c r="E3" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="H3" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="A4" s="5">
+        <v>3</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="5"/>
+      <c r="E4" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="F2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="4">
-        <v>2</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" s="4" t="s">
+      <c r="H4" s="11" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="4">
-        <v>3</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" s="4" t="s">
+    <row r="5" spans="1:15">
+      <c r="A5" s="5">
+        <v>4</v>
+      </c>
+      <c r="B5" s="10" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="4">
-        <v>4</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" s="4" t="s">
+      <c r="C5" s="5" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="4">
-        <v>5</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" s="4"/>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="5">
-        <v>6</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" s="4"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" s="4">
-        <v>7</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="D5" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" s="13"/>
+      <c r="H5" s="13"/>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="A6" s="1"/>
+      <c r="K6"/>
+      <c r="L6"/>
+      <c r="M6"/>
+      <c r="N6"/>
+      <c r="O6"/>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="A7" s="1"/>
+      <c r="K7"/>
+      <c r="L7"/>
+      <c r="M7"/>
+      <c r="N7"/>
+      <c r="O7"/>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="A8" s="1"/>
+      <c r="K8"/>
+      <c r="L8"/>
+      <c r="M8"/>
+      <c r="N8"/>
+      <c r="O8"/>
+    </row>
+    <row r="10" spans="1:15">
       <c r="J10"/>
       <c r="K10"/>
       <c r="L10"/>
@@ -1031,7 +1963,7 @@
       <c r="N10"/>
       <c r="O10"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15">
       <c r="J11"/>
       <c r="K11"/>
       <c r="L11"/>
@@ -1039,7 +1971,7 @@
       <c r="N11"/>
       <c r="O11"/>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15">
       <c r="J12"/>
       <c r="K12"/>
       <c r="L12"/>
@@ -1047,7 +1979,7 @@
       <c r="N12"/>
       <c r="O12"/>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15">
       <c r="J13"/>
       <c r="K13"/>
       <c r="L13"/>
@@ -1055,15 +1987,15 @@
       <c r="N13"/>
       <c r="O13"/>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="s">
-        <v>30</v>
+    <row r="14" spans="1:15">
+      <c r="A14" s="14" t="s">
+        <v>33</v>
       </c>
       <c r="B14" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="J14"/>
       <c r="K14"/>
@@ -1072,13 +2004,17 @@
       <c r="N14"/>
       <c r="O14"/>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15">
       <c r="B15" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="C15" t="s">
-        <v>33</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="F15"/>
+      <c r="G15"/>
+      <c r="H15"/>
+      <c r="I15"/>
       <c r="J15"/>
       <c r="K15"/>
       <c r="L15"/>
@@ -1086,13 +2022,17 @@
       <c r="N15"/>
       <c r="O15"/>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15">
       <c r="B16" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C16" t="s">
-        <v>35</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="F16"/>
+      <c r="G16"/>
+      <c r="H16"/>
+      <c r="I16"/>
       <c r="J16"/>
       <c r="K16"/>
       <c r="L16"/>
@@ -1100,13 +2040,17 @@
       <c r="N16"/>
       <c r="O16"/>
     </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:15">
       <c r="B17" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C17" t="s">
-        <v>37</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="F17"/>
+      <c r="G17"/>
+      <c r="H17"/>
+      <c r="I17"/>
       <c r="J17"/>
       <c r="K17"/>
       <c r="L17"/>
@@ -1114,13 +2058,17 @@
       <c r="N17"/>
       <c r="O17"/>
     </row>
-    <row r="18" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:15">
       <c r="B18" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C18" t="s">
-        <v>39</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="F18"/>
+      <c r="G18"/>
+      <c r="H18"/>
+      <c r="I18"/>
       <c r="J18"/>
       <c r="K18"/>
       <c r="L18"/>
@@ -1128,13 +2076,17 @@
       <c r="N18"/>
       <c r="O18"/>
     </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:15">
       <c r="B19" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C19" t="s">
-        <v>41</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="F19"/>
+      <c r="G19"/>
+      <c r="H19"/>
+      <c r="I19"/>
       <c r="J19"/>
       <c r="K19"/>
       <c r="L19"/>
@@ -1142,13 +2094,17 @@
       <c r="N19"/>
       <c r="O19"/>
     </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:15">
       <c r="B20" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C20" t="s">
-        <v>43</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="F20"/>
+      <c r="G20"/>
+      <c r="H20"/>
+      <c r="I20"/>
       <c r="J20"/>
       <c r="K20"/>
       <c r="L20"/>
@@ -1156,13 +2112,17 @@
       <c r="N20"/>
       <c r="O20"/>
     </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:15">
       <c r="B21" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C21" t="s">
-        <v>45</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="F21"/>
+      <c r="G21"/>
+      <c r="H21"/>
+      <c r="I21"/>
       <c r="J21"/>
       <c r="K21"/>
       <c r="L21"/>
@@ -1170,252 +2130,303 @@
       <c r="N21"/>
       <c r="O21"/>
     </row>
-    <row r="22" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:15">
       <c r="B22" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C22" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="23" spans="2:15" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+      <c r="I22"/>
+      <c r="J22"/>
+      <c r="K22"/>
+      <c r="L22"/>
+      <c r="M22"/>
+      <c r="N22"/>
+      <c r="O22"/>
+    </row>
+    <row r="23" spans="2:15">
       <c r="B23" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C23" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+      <c r="I23"/>
+      <c r="J23"/>
+      <c r="K23"/>
+      <c r="L23"/>
+      <c r="M23"/>
+      <c r="N23"/>
+      <c r="O23"/>
+    </row>
+    <row r="24" spans="2:15">
       <c r="B24" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C24" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="25" spans="2:15" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+      <c r="I24"/>
+      <c r="J24"/>
+      <c r="K24"/>
+      <c r="L24"/>
+      <c r="M24"/>
+      <c r="N24"/>
+      <c r="O24"/>
+    </row>
+    <row r="25" spans="2:15">
       <c r="B25" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C25" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="26" spans="2:15" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+      <c r="I25"/>
+      <c r="J25"/>
+      <c r="K25"/>
+      <c r="L25"/>
+      <c r="M25"/>
+      <c r="N25"/>
+      <c r="O25"/>
+    </row>
+    <row r="26" spans="2:15">
       <c r="B26" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C26" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="27" spans="2:15" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+      <c r="I26"/>
+      <c r="J26"/>
+      <c r="K26"/>
+      <c r="L26"/>
+      <c r="M26"/>
+      <c r="N26"/>
+      <c r="O26"/>
+    </row>
+    <row r="27" spans="2:15">
       <c r="B27" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C27" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="29" spans="2:15" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+      <c r="I27"/>
+      <c r="J27"/>
+      <c r="K27"/>
+      <c r="L27"/>
+      <c r="M27"/>
+      <c r="N27"/>
+      <c r="O27"/>
+    </row>
+    <row r="29" spans="2:15">
       <c r="B29" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="30" spans="2:15" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="30" spans="2:15">
       <c r="B30" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="31" spans="2:15" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="31" spans="2:15">
       <c r="B31" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B33" s="7" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="35" spans="2:2" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2">
+      <c r="B33" s="14" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2">
       <c r="B35" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
-  <dataValidations count="13">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="B2" xr:uid="{00000000-0002-0000-0000-000000000000}">
+  <dataValidations count="14">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="E2">
       <formula1>"TA1-TAG1-产物板-2B01"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2">
+      <formula1>"TA1-枪头_200ul-A05,TA1-枪头_1000ul-A05,TA1-枪头_500ul-A05"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2">
+      <formula1>"TA1-枪头_200ul-B05,TA1-枪头_1000ul-B05,TA1-枪头_500ul-B05"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2">
+      <formula1>"24孔,96孔,8孔"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3">
       <formula1>"TA1-过滤板-2A01"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3">
+      <formula1>"TA1-枪头_200ul-A04,TA1-枪头_1000ul-A04,TA1-枪头_500ul-A04"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3">
+      <formula1>"TA1-枪头_200ul-B04,TA1-枪头_1000ul-B04,TA1-枪头_500ul-B04"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E4">
       <formula1>"TA1-磁子分装_900ul-1,TA1-磁子分装_20ml-1,TA1-磁子分装_2ml-1,TA1-磁子分装_4ml-1,TA1-磁子分装_8ml-1"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B5" xr:uid="{00000000-0002-0000-0000-000003000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B5:C5 F2:F4 B2:D4">
+      <formula1>"TA1-试剂板-A02,TA1-试剂板-A03,TA1-试剂板-B02,TA1-试剂板-B03,TA2-试剂板-A02,TA2-试剂板-A03,TA2-试剂板-B02,TA2-试剂板-B03,TA3-试剂板-A02,TA3-试剂板-A03,TA3-试剂板-B02,TA3-试剂板-B03"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D5">
+      <formula1>"TA1-称量载具_8ml-2"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E5">
       <formula1>"TA1-称量载具_900ul-1,TA1-称量载具_2ml-1,TA1-称量载具_4ml-1,TA1-称量载具_8ml-1,TA1-称量载具_20ml-1"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2" xr:uid="{00000000-0002-0000-0000-000004000000}">
-      <formula1>"24孔,96孔"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="F5">
+      <formula1>"TA1-试剂板-A02,TA1-试剂板-A03,TA1-试剂板-B02,TA1-试剂板-B03,TA2-试剂板-A02,TA2-试剂板-A03,TA2-试剂板-B02,TA2-试剂板-B03,TA3-试剂板-A02,TA3-试剂板-A03,TA3-试剂板-B02,TA3-试剂板-B03"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B6" xr:uid="{00000000-0002-0000-0000-000005000000}">
-      <formula1>"TA1-称量载具_8ml-2"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B7" xr:uid="{00000000-0002-0000-0000-000006000000}">
-      <formula1>"TA1-板盖-A01"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B8" xr:uid="{00000000-0002-0000-0000-000007000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G4:G5">
       <formula1>"TA1-金属板-B01"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:D7" xr:uid="{00000000-0002-0000-0000-000008000000}">
-      <formula1>"TA1-试剂板-A02,TA1-试剂板-A03,TA1-试剂板-B02,TA1-试剂板-B03,TA2-试剂板-A02,TA2-试剂板-A03,TA2-试剂板-B02,TA2-试剂板-B03,TA3-试剂板-A02,TA3-试剂板-A03,TA3-试剂板-B02,TA3-试剂板-B03"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2" xr:uid="{00000000-0002-0000-0000-000009000000}">
-      <formula1>"TA1-枪头_200ul-A04,TA1-枪头_1000ul-A04,TA1-枪头_500ul-A04"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3" xr:uid="{00000000-0002-0000-0000-00000A000000}">
-      <formula1>"TA1-枪头_200ul-B04,TA1-枪头_1000ul-B04,TA1-枪头_500ul-B04"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E4" xr:uid="{00000000-0002-0000-0000-00000B000000}">
-      <formula1>"TA1-枪头_200ul-A05,TA1-枪头_1000ul-A05,TA1-枪头_500ul-A05"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E5" xr:uid="{00000000-0002-0000-0000-00000C000000}">
-      <formula1>"TA1-枪头_200ul-B05,TA1-枪头_1000ul-B05,TA1-枪头_500ul-B05"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H4:H5">
+      <formula1>"TA1-板盖-A01"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultColWidth="10.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="10.2857142857143" defaultRowHeight="15" outlineLevelRow="5" outlineLevelCol="5"/>
   <cols>
-    <col min="2" max="6" width="13.85546875" style="8" customWidth="1"/>
+    <col min="2" max="6" width="13.8571428571429" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:6">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="3">
+      <c r="D1" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="4">
         <v>1</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="4">
+      <c r="B2" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="5">
         <v>2</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="4">
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="5">
         <v>3</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="4">
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="5">
         <v>4</v>
       </c>
-      <c r="B5" s="5"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="4">
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="5">
         <v>5</v>
       </c>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C6" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:C6" etc:filterBottomFollowUsedRange="0">
+    <extLst/>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="1" outlineLevelCol="5"/>
   <cols>
-    <col min="2" max="7" width="13.7109375" style="8" customWidth="1"/>
+    <col min="2" max="7" width="13.7142857142857" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:6">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="3">
+      <c r="D1" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="4">
         <v>1</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/逆合成/Materials-stack4列.xlsx
+++ b/逆合成/Materials-stack4列.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\llwc\Documents\WXWork\1688856998559207\Cache\File\2026-09\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\24017\Downloads\excel_generation_b\逆合成\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C68515C-2B5A-4A05-B232-7056515C87CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="21555" windowHeight="10635" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PlateStack" sheetId="1" r:id="rId1"/>
@@ -71,7 +72,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>TA1-</t>
     </r>
@@ -89,7 +90,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>-2A01</t>
     </r>
@@ -115,7 +116,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>-A03</t>
     </r>
@@ -159,7 +160,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>-A02</t>
     </r>
@@ -185,7 +186,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>-A03</t>
     </r>
@@ -208,7 +209,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>-B02</t>
     </r>
@@ -231,7 +232,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>-B03</t>
     </r>
@@ -378,14 +379,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="26">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -396,13 +391,13 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -417,164 +412,24 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="36">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -599,194 +454,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="13">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -852,251 +521,9 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1106,7 +533,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1129,90 +555,160 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
       <border>
@@ -1223,7 +719,7 @@
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="0"/>
       </font>
       <fill>
@@ -1251,154 +747,40 @@
           <color theme="4"/>
         </bottom>
         <horizontal style="thin">
-          <color theme="4" tint="0.399975585192419"/>
+          <color theme="4" tint="0.39994506668294322"/>
         </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
       </border>
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="6"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="totalRow" dxfId="4"/>
-      <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+      <tableStyleElement type="wholeTable" dxfId="16"/>
+      <tableStyleElement type="headerRow" dxfId="15"/>
+      <tableStyleElement type="totalRow" dxfId="14"/>
+      <tableStyleElement type="firstColumn" dxfId="13"/>
+      <tableStyleElement type="lastColumn" dxfId="12"/>
+      <tableStyleElement type="firstRowStripe" dxfId="11"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="10"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="16"/>
-      <tableStyleElement type="totalRow" dxfId="15"/>
-      <tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
-      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="9"/>
+      <tableStyleElement type="totalRow" dxfId="8"/>
+      <tableStyleElement type="firstRowStripe" dxfId="7"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="6"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="5"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="4"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="3"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="2"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="1"/>
+      <tableStyleElement type="pageFieldValues" dxfId="0"/>
     </tableStyle>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1656,150 +1038,150 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N35"/>
-  <sheetFormatPr defaultColWidth="10.2857142857143" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="10.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="33.7142857142857" style="5" customWidth="1"/>
-    <col min="3" max="3" width="21.2857142857143" style="5" customWidth="1"/>
-    <col min="4" max="4" width="22.2857142857143" style="5" customWidth="1"/>
-    <col min="5" max="5" width="21.7142857142857" style="5" customWidth="1"/>
-    <col min="6" max="8" width="15.2857142857143" style="5" customWidth="1"/>
-    <col min="9" max="9" width="15.4285714285714" style="5" customWidth="1"/>
-    <col min="10" max="10" width="26.8571428571429" style="5" customWidth="1"/>
-    <col min="11" max="11" width="12.5714285714286" style="5" customWidth="1"/>
-    <col min="12" max="12" width="12.4285714285714" style="5" customWidth="1"/>
-    <col min="13" max="13" width="17.5714285714286" style="5" customWidth="1"/>
-    <col min="14" max="14" width="14.2857142857143" style="5" customWidth="1"/>
+    <col min="2" max="2" width="33.7109375" style="4" customWidth="1"/>
+    <col min="3" max="3" width="21.28515625" style="4" customWidth="1"/>
+    <col min="4" max="4" width="22.28515625" style="4" customWidth="1"/>
+    <col min="5" max="5" width="21.7109375" style="4" customWidth="1"/>
+    <col min="6" max="8" width="15.28515625" style="4" customWidth="1"/>
+    <col min="9" max="9" width="15.42578125" style="4" customWidth="1"/>
+    <col min="10" max="10" width="26.85546875" style="4" customWidth="1"/>
+    <col min="11" max="11" width="12.5703125" style="4" customWidth="1"/>
+    <col min="12" max="12" width="12.42578125" style="4" customWidth="1"/>
+    <col min="13" max="13" width="17.5703125" style="4" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="10" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" ht="16.5" customHeight="1" spans="1:14">
+    <row r="2" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="13" t="s">
         <v>7</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="13" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="13" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="13" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="12"/>
-      <c r="D6" s="12" t="s">
+      <c r="C6" s="11"/>
+      <c r="D6" s="13" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
-      <c r="A7" s="8">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" s="7">
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="13" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>7</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="13" t="s">
         <v>22</v>
       </c>
       <c r="H8"/>
       <c r="I8"/>
       <c r="J8"/>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>8</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="D9" s="13" t="s">
         <v>23</v>
       </c>
       <c r="H9"/>
       <c r="I9"/>
       <c r="J9"/>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="H10"/>
       <c r="I10"/>
       <c r="J10"/>
@@ -1808,7 +1190,7 @@
       <c r="M10"/>
       <c r="N10"/>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="H11"/>
       <c r="I11"/>
       <c r="J11"/>
@@ -1817,7 +1199,7 @@
       <c r="M11"/>
       <c r="N11"/>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="H12"/>
       <c r="I12"/>
       <c r="J12"/>
@@ -1826,7 +1208,7 @@
       <c r="M12"/>
       <c r="N12"/>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="H13"/>
       <c r="I13"/>
       <c r="J13"/>
@@ -1835,8 +1217,8 @@
       <c r="M13"/>
       <c r="N13"/>
     </row>
-    <row r="14" spans="1:14">
-      <c r="A14" s="13" t="s">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" s="12" t="s">
         <v>24</v>
       </c>
       <c r="B14" t="s">
@@ -1853,7 +1235,7 @@
       <c r="M14"/>
       <c r="N14"/>
     </row>
-    <row r="15" spans="1:14">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>27</v>
       </c>
@@ -1868,7 +1250,7 @@
       <c r="M15"/>
       <c r="N15"/>
     </row>
-    <row r="16" spans="1:14">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>29</v>
       </c>
@@ -1882,7 +1264,7 @@
       <c r="M16"/>
       <c r="N16"/>
     </row>
-    <row r="17" spans="2:14">
+    <row r="17" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>31</v>
       </c>
@@ -1896,7 +1278,7 @@
       <c r="M17"/>
       <c r="N17"/>
     </row>
-    <row r="18" spans="2:14">
+    <row r="18" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>33</v>
       </c>
@@ -1910,7 +1292,7 @@
       <c r="M18"/>
       <c r="N18"/>
     </row>
-    <row r="19" spans="2:14">
+    <row r="19" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>35</v>
       </c>
@@ -1928,7 +1310,7 @@
       <c r="M19"/>
       <c r="N19"/>
     </row>
-    <row r="20" spans="2:14">
+    <row r="20" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>37</v>
       </c>
@@ -1946,7 +1328,7 @@
       <c r="M20"/>
       <c r="N20"/>
     </row>
-    <row r="21" spans="2:14">
+    <row r="21" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>39</v>
       </c>
@@ -1964,7 +1346,7 @@
       <c r="M21"/>
       <c r="N21"/>
     </row>
-    <row r="22" spans="2:14">
+    <row r="22" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>41</v>
       </c>
@@ -1979,7 +1361,7 @@
       <c r="M22"/>
       <c r="N22"/>
     </row>
-    <row r="23" spans="2:14">
+    <row r="23" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>43</v>
       </c>
@@ -1994,7 +1376,7 @@
       <c r="M23"/>
       <c r="N23"/>
     </row>
-    <row r="24" spans="2:14">
+    <row r="24" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>45</v>
       </c>
@@ -2009,7 +1391,7 @@
       <c r="M24"/>
       <c r="N24"/>
     </row>
-    <row r="25" spans="2:14">
+    <row r="25" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>47</v>
       </c>
@@ -2024,7 +1406,7 @@
       <c r="M25"/>
       <c r="N25"/>
     </row>
-    <row r="26" spans="2:14">
+    <row r="26" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>49</v>
       </c>
@@ -2039,7 +1421,7 @@
       <c r="M26"/>
       <c r="N26"/>
     </row>
-    <row r="27" spans="2:14">
+    <row r="27" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
         <v>51</v>
       </c>
@@ -2054,7 +1436,7 @@
       <c r="M27"/>
       <c r="N27"/>
     </row>
-    <row r="28" spans="2:14">
+    <row r="28" spans="2:14" x14ac:dyDescent="0.25">
       <c r="H28"/>
       <c r="I28"/>
       <c r="J28"/>
@@ -2063,169 +1445,165 @@
       <c r="M28"/>
       <c r="N28"/>
     </row>
-    <row r="29" spans="2:14">
+    <row r="29" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="30" spans="2:14">
+    <row r="30" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="31" spans="2:14">
+    <row r="31" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="33" spans="2:2">
-      <c r="B33" s="13" t="s">
+    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B33" s="12" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="35" spans="2:2">
+    <row r="35" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
         <v>57</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
   <dataValidations count="12">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="B2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="B2" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"TA1-TAG1-产物板-2B01"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"TA1-枪头_200ul-A04,TA1-枪头_1000ul-A04,TA1-枪头_500ul-A04"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"24孔,96孔"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3" xr:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>"TA1-过滤板-2A01"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3" xr:uid="{00000000-0002-0000-0000-000004000000}">
       <formula1>"TA1-枪头_200ul-B04,TA1-枪头_1000ul-B04,TA1-枪头_500ul-B04"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4" xr:uid="{00000000-0002-0000-0000-000005000000}">
       <formula1>"TA1-磁子分装_900ul-1,TA1-磁子分装_20ml-1,TA1-磁子分装_2ml-1,TA1-磁子分装_4ml-1,TA1-磁子分装_8ml-1"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C4">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C4" xr:uid="{00000000-0002-0000-0000-000006000000}">
       <formula1>"TA1-枪头_200ul-A05,TA1-枪头_1000ul-A05,TA1-枪头_500ul-A05"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B5">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B5" xr:uid="{00000000-0002-0000-0000-000007000000}">
       <formula1>"TA1-称量载具_900ul-1,TA1-称量载具_2ml-1,TA1-称量载具_4ml-1,TA1-称量载具_8ml-1,TA1-称量载具_20ml-1"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B6">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B6" xr:uid="{00000000-0002-0000-0000-000008000000}">
       <formula1>"TA1-板盖-A01"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B7">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B7" xr:uid="{00000000-0002-0000-0000-000009000000}">
       <formula1>"TA1-金属板-B01"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D8 D9 D2:D7">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D8 D9 D2:D7" xr:uid="{00000000-0002-0000-0000-00000A000000}">
       <formula1>"TA1-试剂板-A02,TA1-试剂板-A03,TA1-试剂板-B02,TA1-试剂板-B03,TA2-试剂板-A02,TA2-试剂板-A03,TA2-试剂板-B02,TA2-试剂板-B03,TA3-试剂板-A02,TA3-试剂板-A03,TA3-试剂板-B02,TA3-试剂板-B03"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C5:C6">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C5:C6" xr:uid="{00000000-0002-0000-0000-00000B000000}">
       <formula1>"TA1-枪头_200ul-B05,TA1-枪头_1000ul-B05,TA1-枪头_50ul-B05"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultColWidth="10.2857142857143" defaultRowHeight="15" outlineLevelRow="5" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="10.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="6" width="13.8571428571429" style="5" customWidth="1"/>
+    <col min="2" max="6" width="13.85546875" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="5" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="7">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="6">
         <v>1</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-    </row>
-    <row r="3" spans="1:6">
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
-    </row>
-    <row r="4" spans="1:6">
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-    </row>
-    <row r="5" spans="1:6">
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>4</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-    </row>
-    <row r="6" spans="1:6">
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:C6" etc:filterBottomFollowUsedRange="0">
-    <extLst/>
-  </autoFilter>
+  <autoFilter ref="A1:C6" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A2:C9"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -2236,8 +1614,8 @@
         <v>64</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>65</v>
       </c>
       <c r="B3" s="2" t="s">
@@ -2247,8 +1625,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -2258,18 +1636,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>67</v>
       </c>
@@ -2280,7 +1658,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>68</v>
       </c>
@@ -2289,7 +1667,7 @@
       </c>
       <c r="C7" s="2"/>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>12</v>
       </c>
@@ -2298,53 +1676,53 @@
       </c>
       <c r="C8" s="2"/>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
   <dataValidations count="12">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:C2 A3:B3 C7 A4:A7">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:C2 A3:B3 C7 A4:A7" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"TA1-试剂板-A02,TA1-试剂板-A03,TA1-试剂板-B02,TA1-试剂板-B03,TA2-试剂板-A02,TA2-试剂板-A03,TA2-试剂板-B02,TA2-试剂板-B03,TA3-试剂板-A02,TA3-试剂板-A03,TA3-试剂板-B02,TA3-试剂板-B03"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3" xr:uid="{00000000-0002-0000-0200-000001000000}">
       <formula1>"TA1-枪头_200ul-A04,TA1-枪头_1000ul-A04,TA1-枪头_500ul-A04"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="B4">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="B4" xr:uid="{00000000-0002-0000-0200-000002000000}">
       <formula1>"TA1-TAG1-产物板-2B01"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C4">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C4" xr:uid="{00000000-0002-0000-0200-000003000000}">
       <formula1>"TA1-枪头_200ul-B04,TA1-枪头_1000ul-B04,TA1-枪头_500ul-B04"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B5">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B5" xr:uid="{00000000-0002-0000-0200-000004000000}">
       <formula1>"TA1-过滤板-2A01"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C5">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C5" xr:uid="{00000000-0002-0000-0200-000005000000}">
       <formula1>"TA1-枪头_200ul-A05,TA1-枪头_1000ul-A05,TA1-枪头_500ul-A05"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B6">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B6" xr:uid="{00000000-0002-0000-0200-000006000000}">
       <formula1>"TA1-称量载具_900ul-1,TA1-称量载具_2ml-1,TA1-称量载具_4ml-1,TA1-称量载具_8ml-1,TA1-称量载具_20ml-1"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C6">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C6" xr:uid="{00000000-0002-0000-0200-000007000000}">
       <formula1>"TA1-枪头_200ul-B05,TA1-枪头_1000ul-B05,TA1-枪头_500ul-B05"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B7">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B7" xr:uid="{00000000-0002-0000-0200-000008000000}">
       <formula1>"TA1-称量载具_8ml-2"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A8">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A8" xr:uid="{00000000-0002-0000-0200-000009000000}">
       <formula1>"TA1-磁子分装_900ul-1,TA1-磁子分装_20ml-1,TA1-磁子分装_2ml-1,TA1-磁子分装_4ml-1,TA1-磁子分装_8ml-1"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B8">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B8" xr:uid="{00000000-0002-0000-0200-00000A000000}">
       <formula1>"TA1-板盖-A01"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A9">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A9" xr:uid="{00000000-0002-0000-0200-00000B000000}">
       <formula1>"TA1-金属板-B01"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>